--- a/artfynd/A 60587-2025 artfynd.xlsx
+++ b/artfynd/A 60587-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2130,45 +2130,51 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130111287</v>
+        <v>137005359</v>
       </c>
       <c r="B14" t="n">
-        <v>97986</v>
+        <v>56866</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221946</v>
+        <v>205998</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470734</v>
+        <v>470640</v>
       </c>
       <c r="R14" t="n">
-        <v>6539068</v>
+        <v>6539103</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2195,22 +2201,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2235,6 +2241,118 @@
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137005359</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130111287</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>470734</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6539068</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130111287</t>
         </is>
@@ -2255,6 +2373,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60587-2025 artfynd.xlsx
+++ b/artfynd/A 60587-2025 artfynd.xlsx
@@ -2133,7 +2133,7 @@
         <v>137005359</v>
       </c>
       <c r="B14" t="n">
-        <v>56866</v>
+        <v>56879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 60587-2025 artfynd.xlsx
+++ b/artfynd/A 60587-2025 artfynd.xlsx
@@ -2133,7 +2133,7 @@
         <v>137005359</v>
       </c>
       <c r="B14" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 60587-2025 artfynd.xlsx
+++ b/artfynd/A 60587-2025 artfynd.xlsx
@@ -2155,11 +2155,7 @@
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>autobox</t>

--- a/artfynd/A 60587-2025 artfynd.xlsx
+++ b/artfynd/A 60587-2025 artfynd.xlsx
@@ -2133,7 +2133,7 @@
         <v>137005359</v>
       </c>
       <c r="B14" t="n">
-        <v>56881</v>
+        <v>56891</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 60587-2025 artfynd.xlsx
+++ b/artfynd/A 60587-2025 artfynd.xlsx
@@ -2133,7 +2133,7 @@
         <v>137005359</v>
       </c>
       <c r="B14" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 60587-2025 artfynd.xlsx
+++ b/artfynd/A 60587-2025 artfynd.xlsx
@@ -2133,7 +2133,7 @@
         <v>137005359</v>
       </c>
       <c r="B14" t="n">
-        <v>56892</v>
+        <v>56895</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
